--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/WASHINGTON_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/WASHINGTON_2010.xlsx
@@ -3084,7 +3084,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C152">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C625">
@@ -13074,7 +13074,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C707">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C740">
@@ -18834,7 +18834,7 @@
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1027">
